--- a/てきword.xlsx
+++ b/てきword.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B1EACE-EF33-4651-81AE-1D52504F6BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00C56CC-25FE-42E0-82CB-9D278D4523E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-984" yWindow="0" windowWidth="16200" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -932,17 +932,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="16.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
@@ -950,7 +949,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -963,14 +962,14 @@
       <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -983,14 +982,14 @@
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1004,7 +1003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -1018,7 +1017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
@@ -1032,7 +1031,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
@@ -1046,7 +1045,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -1060,7 +1059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
@@ -1074,7 +1073,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>52</v>
       </c>
@@ -1088,7 +1087,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>60</v>
       </c>
@@ -1102,7 +1101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>62</v>
       </c>
@@ -1116,7 +1115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>64</v>
       </c>
@@ -1130,7 +1129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>80</v>
       </c>
@@ -1144,7 +1143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>82</v>
       </c>
@@ -1158,7 +1157,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>83</v>
       </c>
